--- a/output/nhl_2026_27_projections_v3.xlsx
+++ b/output/nhl_2026_27_projections_v3.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,30 +638,35 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Overlay dElo</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>FairOdds Cup (US)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Contrib Elo/xG</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Contrib Goaltending</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Contrib Age</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Contrib Roster</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Contrib Finishing/PP</t>
         </is>
@@ -673,68 +678,71 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Colorado Avalanche</t>
+          <t>Carolina Hurricanes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>109.0359</v>
+        <v>107.6031</v>
       </c>
       <c r="F2" t="n">
-        <v>12.63333571576132</v>
+        <v>12.63599371730306</v>
       </c>
       <c r="G2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H2" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8975</v>
+        <v>0.8436</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3813</v>
+        <v>0.4137</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2128</v>
+        <v>0.192</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1197</v>
+        <v>0.1132</v>
       </c>
       <c r="N2" t="n">
-        <v>10.43058285193634</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>+735</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>14.53741765167042</v>
+        <v>8.287039933520225</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>+783</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>-1.301203426971305</v>
+        <v>14.86116182018452</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.546832861222726</v>
+        <v>-0.1669627848400201</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9853425117174447</v>
+        <v>-0.2526154518856217</v>
       </c>
       <c r="T2" t="n">
-        <v>1.035664354688619</v>
+        <v>0.2384111455252166</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.298489907419239</v>
       </c>
     </row>
     <row r="3">
@@ -743,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carolina Hurricanes</t>
+          <t>Colorado Avalanche</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108.0509</v>
+        <v>107.416</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6028089039399</v>
+        <v>12.75622264314998</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
         <v>108</v>
@@ -772,39 +780,42 @@
         <v>128</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8504</v>
+        <v>0.8702</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4407</v>
+        <v>0.3424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1941</v>
+        <v>0.1886</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1123</v>
+        <v>0.1036</v>
       </c>
       <c r="N3" t="n">
-        <v>8.287039933520225</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>+790</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>14.86116182018452</v>
+        <v>10.43058285193634</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>+865</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1669627848400201</v>
+        <v>14.53741765167042</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2526154518856217</v>
+        <v>-1.301203426971305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2384111455252166</v>
+        <v>-1.546832861222726</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.298489907419239</v>
+        <v>0.9853425117174447</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.035664354688619</v>
       </c>
     </row>
     <row r="4">
@@ -827,53 +838,56 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105.2929</v>
+        <v>105.0989</v>
       </c>
       <c r="F4" t="n">
-        <v>12.79549459998346</v>
+        <v>12.80805697295036</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H4" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I4" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8587</v>
+        <v>0.8547</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4301</v>
+        <v>0.4173</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1741</v>
+        <v>0.1711</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0892</v>
+        <v>0.0896</v>
       </c>
       <c r="N4" t="n">
         <v>9.436252802325914</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>+1021</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="O4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>+1016</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>7.878868425054467</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1.510102857228626</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>-1.433322523586476</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>0.5725455862707067</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.287817003069557</v>
       </c>
     </row>
@@ -897,13 +911,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>104.9745</v>
+        <v>104.481</v>
       </c>
       <c r="F5" t="n">
-        <v>12.76489498603104</v>
+        <v>12.80072751301606</v>
       </c>
       <c r="G5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" t="n">
         <v>105</v>
@@ -912,38 +926,41 @@
         <v>125</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8268</v>
+        <v>0.8128</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2521</v>
+        <v>0.2499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1507</v>
+        <v>0.1513</v>
       </c>
       <c r="M5" t="n">
-        <v>0.078</v>
+        <v>0.079</v>
       </c>
       <c r="N5" t="n">
         <v>9.85275482151591</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>+1182</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="O5" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>+1166</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>6.138653564716753</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>-0.7357550112599021</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0.02402743531098147</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>1.528262135604438</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>2.926836598332558</v>
       </c>
     </row>
@@ -967,53 +984,56 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>104.4767</v>
+        <v>102.882</v>
       </c>
       <c r="F6" t="n">
-        <v>13.00138303051143</v>
+        <v>13.08393652306117</v>
       </c>
       <c r="G6" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H6" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7624</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2656</v>
+        <v>0.2399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1406</v>
+        <v>0.1235</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0776</v>
+        <v>0.0677</v>
       </c>
       <c r="N6" t="n">
         <v>11.95676267158673</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>+1189</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
+      <c r="O6" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>+1377</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>9.436735107173774</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-0.8022613128825858</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-0.8994067827698127</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>2.111485424037829</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>0.5100934026557666</v>
       </c>
     </row>
@@ -1023,12 +1043,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ottawa Senators</t>
+          <t>Montreal Canadiens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1037,54 +1057,57 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102.9479</v>
+        <v>102.2868</v>
       </c>
       <c r="F7" t="n">
-        <v>12.72368558270287</v>
+        <v>12.77859440656525</v>
       </c>
       <c r="G7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" t="n">
         <v>103</v>
       </c>
       <c r="I7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.7165</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2112</v>
+        <v>0.2122</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1156</v>
+        <v>0.1138</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0611</v>
+        <v>0.0613</v>
       </c>
       <c r="N7" t="n">
-        <v>7.085134171727478</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>+1537</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>8.451268172646309</v>
+        <v>8.510549067215697</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>+1531</t>
+        </is>
       </c>
       <c r="Q7" t="n">
-        <v>1.77019449892022</v>
+        <v>1.740788541281878</v>
       </c>
       <c r="R7" t="n">
-        <v>1.156408289279054</v>
+        <v>2.510899193633914</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3775057526043846</v>
+        <v>2.196737059056645</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.897413578334854</v>
+        <v>0.6120765889048018</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.804633765882705</v>
       </c>
     </row>
     <row r="8">
@@ -1093,12 +1116,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Montreal Canadiens</t>
+          <t>Ottawa Senators</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>OTT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1107,54 +1130,57 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.8642</v>
+        <v>101.9931</v>
       </c>
       <c r="F8" t="n">
-        <v>12.75280446655465</v>
+        <v>12.77485702805353</v>
       </c>
       <c r="G8" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H8" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I8" t="n">
         <v>123</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7307</v>
+        <v>0.7091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2071</v>
+        <v>0.2076</v>
       </c>
       <c r="L8" t="n">
-        <v>0.118</v>
+        <v>0.1091</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0629</v>
+        <v>0.0544</v>
       </c>
       <c r="N8" t="n">
-        <v>8.510549067215697</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>+1490</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1.740788541281878</v>
+        <v>7.085134171727478</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>+1738</t>
+        </is>
       </c>
       <c r="Q8" t="n">
-        <v>2.510899193633914</v>
+        <v>8.451268172646309</v>
       </c>
       <c r="R8" t="n">
-        <v>2.196737059056645</v>
+        <v>1.77019449892022</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6120765889048018</v>
+        <v>1.156408289279054</v>
       </c>
       <c r="T8" t="n">
-        <v>1.804633765882705</v>
+        <v>0.3775057526043846</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-2.897413578334854</v>
       </c>
     </row>
     <row r="9">
@@ -1177,53 +1203,56 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101.1383</v>
+        <v>101.821</v>
       </c>
       <c r="F9" t="n">
-        <v>13.05750446878328</v>
+        <v>13.03574133124793</v>
       </c>
       <c r="G9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7754</v>
+        <v>0.7891</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2862</v>
+        <v>0.3019</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1172</v>
+        <v>0.1269</v>
       </c>
       <c r="M9" t="n">
-        <v>0.058</v>
+        <v>0.0644</v>
       </c>
       <c r="N9" t="n">
         <v>11.11131222666323</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>+1624</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="O9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>+1453</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>3.210989299173198</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-1.056838272229703</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-0.8014174971800627</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1.235756684107004</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>3.501549285384193</v>
       </c>
     </row>
@@ -1233,68 +1262,71 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Minnesota Wild</t>
+          <t>Washington Capitals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>99.91079999999999</v>
+        <v>100.1821</v>
       </c>
       <c r="F10" t="n">
-        <v>12.99066276569095</v>
+        <v>13.00620835353538</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" t="n">
         <v>121</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7131</v>
+        <v>0.6656</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1484</v>
+        <v>0.1955</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0917</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0444</v>
+        <v>0.0486</v>
       </c>
       <c r="N10" t="n">
-        <v>8.309178835527998</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>+2152</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>5.379811289434888</v>
+        <v>8.112523146305424</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>+1958</t>
+        </is>
       </c>
       <c r="Q10" t="n">
-        <v>2.005665298453329</v>
+        <v>2.584596256488481</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.557135023221267</v>
+        <v>-0.6260081131995053</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1951737588436689</v>
+        <v>0.9768030983028069</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4110455514341763</v>
+        <v>0.4846185150012107</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.3329361587306978</v>
       </c>
     </row>
     <row r="11">
@@ -1303,68 +1335,71 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Buffalo Sabres</t>
+          <t>Minnesota Wild</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>98.29049999999999</v>
+        <v>99.093</v>
       </c>
       <c r="F11" t="n">
-        <v>13.03087449555907</v>
+        <v>13.06614034067981</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I11" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5951</v>
+        <v>0.6806</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1311</v>
+        <v>0.1402</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0713</v>
+        <v>0.0851</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0371</v>
+        <v>0.0386</v>
       </c>
       <c r="N11" t="n">
-        <v>7.27216984942758</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>+2595</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>2.836715742326624</v>
+        <v>8.309178835527998</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>+2491</t>
+        </is>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9552625989374606</v>
+        <v>5.379811289434888</v>
       </c>
       <c r="R11" t="n">
-        <v>2.115930602285307</v>
+        <v>2.005665298453329</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1755303680812688</v>
+        <v>-1.557135023221267</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3104022577527606</v>
+        <v>0.1951737588436689</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.4110455514341763</v>
       </c>
     </row>
     <row r="12">
@@ -1373,68 +1408,71 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Washington Capitals</t>
+          <t>Buffalo Sabres</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>96.86109999999999</v>
+        <v>97.38849999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>13.12407828889684</v>
+        <v>13.09418624891796</v>
       </c>
       <c r="G12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" t="n">
         <v>97</v>
       </c>
       <c r="I12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5702</v>
+        <v>0.5673</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1361</v>
+        <v>0.1276</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0602</v>
+        <v>0.0649</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0291</v>
+        <v>0.0329</v>
       </c>
       <c r="N12" t="n">
-        <v>8.112523146305424</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>+3336</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>2.584596256488481</v>
+        <v>7.27216984942758</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>+2940</t>
+        </is>
       </c>
       <c r="Q12" t="n">
-        <v>-0.6260081131995053</v>
+        <v>2.836715742326624</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9768030983028069</v>
+        <v>-0.9552625989374606</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4846185150012107</v>
+        <v>2.115930602285307</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3329361587306978</v>
+        <v>0.1755303680812688</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.3104022577527606</v>
       </c>
     </row>
     <row r="13">
@@ -1457,53 +1495,56 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>96.11369999999999</v>
+        <v>97.0558</v>
       </c>
       <c r="F13" t="n">
-        <v>13.08387141021754</v>
+        <v>13.07049234485885</v>
       </c>
       <c r="G13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6091</v>
+        <v>0.6249</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0931</v>
+        <v>0.1123</v>
       </c>
       <c r="L13" t="n">
-        <v>0.059</v>
+        <v>0.0665</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0261</v>
+        <v>0.03</v>
       </c>
       <c r="N13" t="n">
         <v>8.023130703542428</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>+3731</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>+3233</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
         <v>1.324047952222015</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-0.8057165104439747</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.3491635485265494</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.3460637474461083</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.595226977498551</v>
       </c>
     </row>
@@ -1513,68 +1554,71 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pittsburgh Penguins</t>
+          <t>Boston Bruins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>95.63800000000001</v>
+        <v>95.0716</v>
       </c>
       <c r="F14" t="n">
-        <v>13.1282668749197</v>
+        <v>13.21966525275657</v>
       </c>
       <c r="G14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I14" t="n">
         <v>117</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5385</v>
+        <v>0.5041</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1185</v>
+        <v>0.0954</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0539</v>
+        <v>0.0496</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0267</v>
+        <v>0.023</v>
       </c>
       <c r="N14" t="n">
-        <v>9.661055316871911</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>+3645</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1.69300991771921</v>
+        <v>7.661371017102861</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>+4248</t>
+        </is>
       </c>
       <c r="Q14" t="n">
-        <v>0.4060613738513141</v>
+        <v>-3.00914682888676</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.196782968015675</v>
+        <v>2.155193211030974</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4088803328656631</v>
+        <v>0.9170523381385458</v>
       </c>
       <c r="T14" t="n">
-        <v>1.580288776575413</v>
+        <v>0.1584539766783823</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.404468715186276</v>
       </c>
     </row>
     <row r="15">
@@ -1583,68 +1627,71 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boston Bruins</t>
+          <t>Philadelphia Flyers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>94.8244</v>
+        <v>93.74379999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>13.24421026526516</v>
+        <v>13.23280288779466</v>
       </c>
       <c r="G15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4911</v>
+        <v>0.4719</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0852</v>
+        <v>0.0927</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0458</v>
+        <v>0.0443</v>
       </c>
       <c r="M15" t="n">
-        <v>0.021</v>
+        <v>0.0202</v>
       </c>
       <c r="N15" t="n">
-        <v>7.661371017102861</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>+4662</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>-3.00914682888676</v>
+        <v>6.130068512120818</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>+4850</t>
+        </is>
       </c>
       <c r="Q15" t="n">
-        <v>2.155193211030974</v>
+        <v>0.9320559732546758</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9170523381385458</v>
+        <v>-0.6664783913283208</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1584539766783823</v>
+        <v>1.024346150108006</v>
       </c>
       <c r="T15" t="n">
-        <v>1.404468715186276</v>
+        <v>-0.9700416326965275</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.4277131413355603</v>
       </c>
     </row>
     <row r="16">
@@ -1667,53 +1714,56 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>94.4769</v>
+        <v>93.7159</v>
       </c>
       <c r="F16" t="n">
-        <v>13.06070153485096</v>
+        <v>13.07881847642492</v>
       </c>
       <c r="G16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" t="n">
         <v>115</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5022</v>
+        <v>0.4774</v>
       </c>
       <c r="K16" t="n">
-        <v>0.101</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0474</v>
+        <v>0.044</v>
       </c>
       <c r="M16" t="n">
-        <v>0.021</v>
+        <v>0.0193</v>
       </c>
       <c r="N16" t="n">
         <v>7.139596880634292</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>+4662</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
+      <c r="O16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>+5081</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
         <v>0.1087818044913432</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>1.208731970667257</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.6263597529989886</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.343871583847033</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-0.6087481431724812</v>
       </c>
     </row>
@@ -1723,12 +1773,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Philadelphia Flyers</t>
+          <t>Pittsburgh Penguins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1737,10 +1787,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.04559999999999</v>
+        <v>92.83580000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>13.23411632197187</v>
+        <v>13.22705310541185</v>
       </c>
       <c r="G17" t="n">
         <v>71</v>
@@ -1752,39 +1802,42 @@
         <v>114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4555</v>
+        <v>0.4539</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0813</v>
       </c>
       <c r="L17" t="n">
-        <v>0.039</v>
+        <v>0.0392</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0174</v>
+        <v>0.0199</v>
       </c>
       <c r="N17" t="n">
-        <v>6.130068512120818</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>+5647</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>0.9320559732546758</v>
+        <v>9.661055316871911</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>+4925</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>-0.6664783913283208</v>
+        <v>1.69300991771921</v>
       </c>
       <c r="R17" t="n">
-        <v>1.024346150108006</v>
+        <v>0.4060613738513141</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9700416326965275</v>
+        <v>-2.196782968015675</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4277131413355603</v>
+        <v>0.4088803328656631</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.580288776575413</v>
       </c>
     </row>
     <row r="18">
@@ -1807,53 +1860,56 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91.1065</v>
+        <v>91.96550000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>13.08038483366371</v>
+        <v>13.07311747021494</v>
       </c>
       <c r="G18" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H18" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4486</v>
+        <v>0.4677</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0473</v>
+        <v>0.0559</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0331</v>
+        <v>0.0366</v>
       </c>
       <c r="M18" t="n">
-        <v>0.012</v>
+        <v>0.0133</v>
       </c>
       <c r="N18" t="n">
         <v>6.73886642624792</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>+8233</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
+      <c r="O18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>+7419</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
         <v>-3.157721894707941</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>0.7359649876134507</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>1.103819203348884</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.9004739319240367</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-0.1468758895328413</v>
       </c>
     </row>
@@ -1863,12 +1919,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Anaheim Ducks</t>
+          <t>Los Angeles Kings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>LAK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1877,54 +1933,57 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>90.0641</v>
+        <v>91.5638</v>
       </c>
       <c r="F19" t="n">
-        <v>13.2579322847436</v>
+        <v>13.26660204547431</v>
       </c>
       <c r="G19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J19" t="n">
-        <v>0.46</v>
+        <v>0.5052</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.031</v>
+        <v>0.0387</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0112</v>
+        <v>0.0163</v>
       </c>
       <c r="N19" t="n">
-        <v>6.925373482467831</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>+8829</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.9384647563578424</v>
+        <v>8.389923070792923</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>+6035</t>
+        </is>
       </c>
       <c r="Q19" t="n">
-        <v>-1.060027611444696</v>
+        <v>-0.3252488243687048</v>
       </c>
       <c r="R19" t="n">
-        <v>0.06260369320421667</v>
+        <v>-2.344606770331386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9854056074040981</v>
+        <v>-1.88819993230479</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6381957038129528</v>
+        <v>-0.502265597719503</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.160863096729224</v>
       </c>
     </row>
     <row r="20">
@@ -1933,68 +1992,71 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Jersey Devils</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>NSH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>90.017</v>
+        <v>91.4713</v>
       </c>
       <c r="F20" t="n">
-        <v>13.10742123566436</v>
+        <v>13.24839342346197</v>
       </c>
       <c r="G20" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3664</v>
+        <v>0.4593</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0543</v>
+        <v>0.0526</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0251</v>
+        <v>0.0365</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0106</v>
+        <v>0.0171</v>
       </c>
       <c r="N20" t="n">
-        <v>8.08185262922734</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>+9334</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>0.4608001064918288</v>
+        <v>8.467264727101742</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>+5748</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>-2.606873816955191</v>
+        <v>-4.179712937967621</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4340865829645832</v>
+        <v>3.631881173782457</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6862557804954555</v>
+        <v>-1.750654477351555</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.822809837164811</v>
+        <v>-0.9481233329428844</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.8115534968169447</v>
       </c>
     </row>
     <row r="21">
@@ -2003,68 +2065,71 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Winnipeg Jets</t>
+          <t>New Jersey Devils</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WPG</t>
+          <t>NJD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>89.44580000000001</v>
+        <v>90.82340000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>13.01781121006408</v>
+        <v>13.13901350207011</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4047</v>
+        <v>0.3909</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0357</v>
+        <v>0.0577</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0244</v>
+        <v>0.0301</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0097</v>
+        <v>0.0128</v>
       </c>
       <c r="N21" t="n">
-        <v>8.140000216729245</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>+10209</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>-2.74817447802685</v>
+        <v>8.08185262922734</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>+7712</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>-0.03608817469521482</v>
+        <v>0.4608001064918288</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.183910751078082</v>
+        <v>-2.606873816955191</v>
       </c>
       <c r="S21" t="n">
-        <v>1.080791714011119</v>
+        <v>0.4340865829645832</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09443943429775073</v>
+        <v>0.6862557804954555</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.822809837164811</v>
       </c>
     </row>
     <row r="22">
@@ -2073,12 +2138,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Toronto Maple Leafs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2087,10 +2152,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>89.4348</v>
+        <v>89.83880000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>13.16325476801269</v>
+        <v>13.08096807321894</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -2102,39 +2167,42 @@
         <v>111</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3324</v>
+        <v>0.3466</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0415</v>
+        <v>0.044</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0246</v>
+        <v>0.025</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0102</v>
+        <v>0.0103</v>
       </c>
       <c r="N22" t="n">
-        <v>9.184839315742089</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>+9704</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>0.6979198033265082</v>
+        <v>8.7101896414871</v>
+      </c>
+      <c r="O22" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>+9609</t>
+        </is>
       </c>
       <c r="Q22" t="n">
-        <v>-2.218535999354475</v>
+        <v>-8.193380227493302</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3343300754021691</v>
+        <v>2.580073488194848</v>
       </c>
       <c r="S22" t="n">
-        <v>1.285179068259477</v>
+        <v>-0.7984428608114038</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.142967471019861</v>
+        <v>0.09756098771463831</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.4100984906928617</v>
       </c>
     </row>
     <row r="23">
@@ -2143,27 +2211,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NSH</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.4324</v>
+        <v>89.3768</v>
       </c>
       <c r="F23" t="n">
-        <v>13.27107540421041</v>
+        <v>13.16504286340761</v>
       </c>
       <c r="G23" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H23" t="n">
         <v>89</v>
@@ -2172,39 +2240,42 @@
         <v>111</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3995</v>
+        <v>0.332</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0366</v>
+        <v>0.0463</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0248</v>
+        <v>0.0249</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0114</v>
+        <v>0.0102</v>
       </c>
       <c r="N23" t="n">
-        <v>8.467264727101742</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>+8672</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>-4.179712937967621</v>
+        <v>9.184839315742089</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>+9704</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>3.631881173782457</v>
+        <v>0.6979198033265082</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.750654477351555</v>
+        <v>-2.218535999354475</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9481233329428844</v>
+        <v>0.3343300754021691</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8115534968169447</v>
+        <v>1.285179068259477</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-3.142967471019861</v>
       </c>
     </row>
     <row r="24">
@@ -2213,27 +2284,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Los Angeles Kings</t>
+          <t>Winnipeg Jets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LAK</t>
+          <t>WPG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>88.75920000000001</v>
+        <v>89.19759999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>13.30412399714965</v>
+        <v>13.03733682372077</v>
       </c>
       <c r="G24" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H24" t="n">
         <v>89</v>
@@ -2242,39 +2313,42 @@
         <v>111</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4192</v>
+        <v>0.3867</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0697</v>
+        <v>0.0372</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0268</v>
+        <v>0.0237</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01</v>
+        <v>0.0095</v>
       </c>
       <c r="N24" t="n">
-        <v>8.389923070792923</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>+9900</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>-0.3252488243687048</v>
+        <v>8.140000216729245</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>+10426</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>-2.344606770331386</v>
+        <v>-2.74817447802685</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.88819993230479</v>
+        <v>-0.03608817469521482</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.502265597719503</v>
+        <v>-2.183910751078082</v>
       </c>
       <c r="T24" t="n">
-        <v>0.160863096729224</v>
+        <v>1.080791714011119</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.09443943429775073</v>
       </c>
     </row>
     <row r="25">
@@ -2283,24 +2357,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Detroit Red Wings</t>
+          <t>New York Rangers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>88.6258</v>
+        <v>89.1225</v>
       </c>
       <c r="F25" t="n">
-        <v>13.22600722390203</v>
+        <v>13.40335251852586</v>
       </c>
       <c r="G25" t="n">
         <v>67</v>
@@ -2309,42 +2383,45 @@
         <v>89</v>
       </c>
       <c r="I25" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3103</v>
+        <v>0.3395</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0362</v>
+        <v>0.0522</v>
       </c>
       <c r="L25" t="n">
-        <v>0.021</v>
+        <v>0.0233</v>
       </c>
       <c r="M25" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>7.181298352106282</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>+11665</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>-0.6139854623175383</v>
+        <v>7.823147646950697</v>
+      </c>
+      <c r="O25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>+11011</t>
+        </is>
       </c>
       <c r="Q25" t="n">
-        <v>-2.867146491554658</v>
+        <v>-4.799844584438726</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.5406317062686432</v>
+        <v>-1.908540197038762</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5098561696959281</v>
+        <v>0.4458023315861614</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6547122407183014</v>
+        <v>-0.1363557253125856</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.8318037149568038</v>
       </c>
     </row>
     <row r="26">
@@ -2353,12 +2430,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Jose Sharks</t>
+          <t>Anaheim Ducks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2367,54 +2444,57 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>87.2568</v>
+        <v>87.82940000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>13.05209904532405</v>
+        <v>13.27973383668051</v>
       </c>
       <c r="G26" t="n">
         <v>66</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I26" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3746</v>
+        <v>0.3901</v>
       </c>
       <c r="K26" t="n">
-        <v>0.054</v>
+        <v>0.0617</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0203</v>
+        <v>0.024</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0078</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>7.118157267955309</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>+12721</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>-7.938505026646673</v>
+        <v>6.925373482467831</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>+12558</t>
+        </is>
       </c>
       <c r="Q26" t="n">
-        <v>1.844380847656744</v>
+        <v>-0.9384647563578424</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6190511016808269</v>
+        <v>-1.060027611444696</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.592923819294237</v>
+        <v>0.06260369320421667</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8001028049016089</v>
+        <v>-0.9854056074040981</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.6381957038129528</v>
       </c>
     </row>
     <row r="27">
@@ -2423,68 +2503,71 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New York Rangers</t>
+          <t>Detroit Red Wings</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86.8682</v>
+        <v>86.32299999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>13.38634932290427</v>
+        <v>13.2306982483017</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
       </c>
       <c r="H27" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I27" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2763</v>
+        <v>0.2575</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0372</v>
+        <v>0.027</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0164</v>
+        <v>0.0152</v>
       </c>
       <c r="M27" t="n">
-        <v>0.006</v>
+        <v>0.0051</v>
       </c>
       <c r="N27" t="n">
-        <v>7.823147646950697</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>+16567</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>-4.799844584438726</v>
+        <v>7.181298352106282</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>+19508</t>
+        </is>
       </c>
       <c r="Q27" t="n">
-        <v>-1.908540197038762</v>
+        <v>-0.6139854623175383</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4458023315861614</v>
+        <v>-2.867146491554658</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1363557253125856</v>
+        <v>-0.5406317062686432</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8318037149568038</v>
+        <v>-0.5098561696959281</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.6547122407183014</v>
       </c>
     </row>
     <row r="28">
@@ -2493,24 +2576,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toronto Maple Leafs</t>
+          <t>San Jose Sharks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>86.3905</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>13.08958148545424</v>
+        <v>13.05300494498525</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -2519,42 +2602,45 @@
         <v>86</v>
       </c>
       <c r="I28" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2518</v>
+        <v>0.3378</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0221</v>
+        <v>0.047</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0143</v>
+        <v>0.0179</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0059</v>
+        <v>0.0066</v>
       </c>
       <c r="N28" t="n">
-        <v>8.7101896414871</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>+16849</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>-8.193380227493302</v>
+        <v>7.118157267955309</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>+15052</t>
+        </is>
       </c>
       <c r="Q28" t="n">
-        <v>2.580073488194848</v>
+        <v>-7.938505026646673</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.7984428608114038</v>
+        <v>1.844380847656744</v>
       </c>
       <c r="S28" t="n">
-        <v>0.09756098771463831</v>
+        <v>0.6190511016808269</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4100984906928617</v>
+        <v>-1.592923819294237</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.8001028049016089</v>
       </c>
     </row>
     <row r="29">
@@ -2563,68 +2649,71 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New York Islanders</t>
+          <t>Seattle Kraken</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NYI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>84.90130000000001</v>
+        <v>84.5046</v>
       </c>
       <c r="F29" t="n">
-        <v>13.1690508655738</v>
+        <v>13.2016441090009</v>
       </c>
       <c r="G29" t="n">
         <v>63</v>
       </c>
       <c r="H29" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I29" t="n">
         <v>106</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2313</v>
+        <v>0.2955</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0252</v>
+        <v>0.0382</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0127</v>
+        <v>0.0138</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="N29" t="n">
-        <v>5.904979974439156</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>+19131</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>-3.718975172859124</v>
+        <v>5.794809968760188</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>+18768</t>
+        </is>
       </c>
       <c r="Q29" t="n">
-        <v>0.4615174749515494</v>
+        <v>-8.045932130130696</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.9410552958807847</v>
+        <v>-0.714307744383768</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.333554744482397</v>
+        <v>-0.422391505953313</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.77312184143457</v>
+        <v>-0.8826293784054555</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.413091909101055</v>
       </c>
     </row>
     <row r="30">
@@ -2633,68 +2722,71 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Seattle Kraken</t>
+          <t>New York Islanders</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>84.60469999999999</v>
+        <v>83.2178</v>
       </c>
       <c r="F30" t="n">
-        <v>13.18434756110674</v>
+        <v>13.17292358406345</v>
       </c>
       <c r="G30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H30" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I30" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2991</v>
+        <v>0.1958</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0384</v>
+        <v>0.0185</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0142</v>
+        <v>0.0094</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0047</v>
+        <v>0.0037</v>
       </c>
       <c r="N30" t="n">
-        <v>5.794809968760188</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>+21177</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>-8.045932130130696</v>
+        <v>5.904979974439156</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>+26927</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>-0.714307744383768</v>
+        <v>-3.718975172859124</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.422391505953313</v>
+        <v>0.4615174749515494</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.8826293784054555</v>
+        <v>-0.9410552958807847</v>
       </c>
       <c r="T30" t="n">
-        <v>1.413091909101055</v>
+        <v>-1.333554744482397</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-1.77312184143457</v>
       </c>
     </row>
     <row r="31">
@@ -2703,24 +2795,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Calgary Flames</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>80.54130000000001</v>
+        <v>80.64570000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>12.98494340324664</v>
+        <v>13.13801477595551</v>
       </c>
       <c r="G31" t="n">
         <v>59</v>
@@ -2729,42 +2821,45 @@
         <v>81</v>
       </c>
       <c r="I31" t="n">
-        <v>102</v>
+        <v>102.0499999999993</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1948</v>
+        <v>0.1786</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0226</v>
+        <v>0.0095</v>
       </c>
       <c r="L31" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="N31" t="n">
-        <v>4.091492155309823</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>+38362</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>-7.566996579698094</v>
+        <v>6.748602304917045</v>
+      </c>
+      <c r="O31" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>+41567</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>-0.1681206183302957</v>
+        <v>-14.08048256211883</v>
       </c>
       <c r="R31" t="n">
-        <v>0.4355320155673481</v>
+        <v>-0.4221108765379712</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.9345974485237442</v>
+        <v>2.496371645999701</v>
       </c>
       <c r="T31" t="n">
-        <v>-3.769962061404637</v>
+        <v>-0.8766338907976194</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-1.025233403433248</v>
       </c>
     </row>
     <row r="32">
@@ -2773,12 +2868,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vancouver Canucks</t>
+          <t>Calgary Flames</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2787,10 +2882,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>79.92449999999999</v>
+        <v>80.34690000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>12.93511234830012</v>
+        <v>12.98744885544414</v>
       </c>
       <c r="G32" t="n">
         <v>59</v>
@@ -2799,42 +2894,45 @@
         <v>80</v>
       </c>
       <c r="I32" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1876</v>
+        <v>0.1905</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0174</v>
+        <v>0.0212</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0067</v>
+        <v>0.0086</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
       <c r="N32" t="n">
-        <v>5.049701439462</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>+66567</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>-12.95704996163819</v>
+        <v>4.091492155309823</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>+33233</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>0.6421783467345122</v>
+        <v>-7.566996579698094</v>
       </c>
       <c r="R32" t="n">
-        <v>1.894374713769438</v>
+        <v>-0.1681206183302957</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.9710337202305506</v>
+        <v>0.4355320155673481</v>
       </c>
       <c r="T32" t="n">
-        <v>-1.215026643377131</v>
+        <v>-0.9345974485237442</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-3.769962061404637</v>
       </c>
     </row>
     <row r="33">
@@ -2843,24 +2941,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Vancouver Canucks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>77.7753</v>
+        <v>78.35809999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>13.10386893433023</v>
+        <v>12.89331951666505</v>
       </c>
       <c r="G33" t="n">
         <v>57</v>
@@ -2872,39 +2970,42 @@
         <v>99</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1313</v>
+        <v>0.1563</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0055</v>
+        <v>0.0136</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0037</v>
+        <v>0.0054</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0011</v>
+        <v>0.0018</v>
       </c>
       <c r="N33" t="n">
-        <v>6.748602304917045</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>+90809</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>-14.08048256211883</v>
+        <v>5.049701439462</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>+55456</t>
+        </is>
       </c>
       <c r="Q33" t="n">
-        <v>-0.4221108765379712</v>
+        <v>-12.95704996163819</v>
       </c>
       <c r="R33" t="n">
-        <v>2.496371645999701</v>
+        <v>0.6421783467345122</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.8766338907976194</v>
+        <v>1.894374713769438</v>
       </c>
       <c r="T33" t="n">
-        <v>-1.025233403433248</v>
+        <v>-0.9710337202305506</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-1.215026643377131</v>
       </c>
     </row>
   </sheetData>
@@ -2918,7 +3019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2994,30 +3095,35 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Overlay dElo</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>FairOdds Cup (US)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Contrib Elo/xG</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Contrib Goaltending</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Contrib Age</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Contrib Roster</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Contrib Finishing/PP</t>
         </is>
@@ -3043,53 +3149,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105.5253</v>
+        <v>105.0575</v>
       </c>
       <c r="F2" t="n">
-        <v>12.72591665875117</v>
+        <v>12.74610685950841</v>
       </c>
       <c r="G2" t="n">
         <v>84</v>
       </c>
       <c r="H2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I2" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8028</v>
+        <v>0.7953</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3256</v>
+        <v>0.3254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1643</v>
+        <v>0.1587</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0917</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>8.510549067215697</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>+991</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
+      <c r="O2" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>+1019</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>1.663285321400089</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>2.210608415943441</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>3.902076166830055</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>0.7088738271955537</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>2.410309221640793</v>
       </c>
     </row>
@@ -3099,24 +3208,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colorado Avalanche</t>
+          <t>Carolina Hurricanes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>104.8576</v>
+        <v>104.2199</v>
       </c>
       <c r="F3" t="n">
-        <v>13.04011988873842</v>
+        <v>12.87859968408764</v>
       </c>
       <c r="G3" t="n">
         <v>83</v>
@@ -3125,42 +3234,45 @@
         <v>105</v>
       </c>
       <c r="I3" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8103</v>
+        <v>0.7832</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3077</v>
+        <v>0.3358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1637</v>
+        <v>0.1502</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0922</v>
+        <v>0.0861</v>
       </c>
       <c r="N3" t="n">
-        <v>10.43058285193634</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>+985</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>12.22169934065773</v>
+        <v>8.287039933520225</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>+1061</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2402753669340649</v>
+        <v>12.58913402073155</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.240137786594671</v>
+        <v>-0.2047537383752678</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2461528725395291</v>
+        <v>-0.4532944291872982</v>
       </c>
       <c r="T3" t="n">
-        <v>1.14462532367806</v>
+        <v>-0.5184506489398766</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-1.400998814443474</v>
       </c>
     </row>
     <row r="4">
@@ -3169,68 +3281,71 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carolina Hurricanes</t>
+          <t>Colorado Avalanche</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>104.6226</v>
+        <v>103.4027</v>
       </c>
       <c r="F4" t="n">
-        <v>12.84276694899859</v>
+        <v>13.12493653721459</v>
       </c>
       <c r="G4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I4" t="n">
         <v>125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7896</v>
+        <v>0.7744</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3543</v>
+        <v>0.2748</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1553</v>
+        <v>0.1429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>8.287039933520225</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>+1012</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>12.58913402073155</v>
+        <v>10.43058285193634</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>+1171</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2047537383752678</v>
+        <v>12.22169934065773</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.4532944291872982</v>
+        <v>-0.2402753669340649</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5184506489398766</v>
+        <v>-3.240137786594671</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.400998814443474</v>
+        <v>0.2461528725395291</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.14462532367806</v>
       </c>
     </row>
     <row r="5">
@@ -3253,53 +3368,56 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103.4875</v>
+        <v>103.0539</v>
       </c>
       <c r="F5" t="n">
-        <v>12.95690672549545</v>
+        <v>12.98823560828882</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H5" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I5" t="n">
         <v>124</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7846</v>
+        <v>0.7711</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2615</v>
+        <v>0.2549</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1448</v>
+        <v>0.1396</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0788</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>9.85275482151591</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>+1169</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="O5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>+1219</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>5.259540278955885</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>-0.4288042731975485</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>-0.5051812172356003</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.01301292053522001</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>4.374820086135516</v>
       </c>
     </row>
@@ -3323,10 +3441,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102.5596</v>
+        <v>102.4158</v>
       </c>
       <c r="F6" t="n">
-        <v>12.83831492342384</v>
+        <v>12.87248540290665</v>
       </c>
       <c r="G6" t="n">
         <v>81</v>
@@ -3338,38 +3456,41 @@
         <v>123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7865</v>
+        <v>0.7815</v>
       </c>
       <c r="K6" t="n">
-        <v>0.327</v>
+        <v>0.3261</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1382</v>
+        <v>0.1381</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0703</v>
+        <v>0.0698</v>
       </c>
       <c r="N6" t="n">
         <v>9.436252802325914</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>+1322</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
+      <c r="O6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>+1333</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>6.547054304846505</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>1.300625377297377</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-2.324824196364521</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>0.01530559815326566</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>2.074648572366752</v>
       </c>
     </row>
@@ -3393,53 +3514,56 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101.1048</v>
+        <v>101.733</v>
       </c>
       <c r="F7" t="n">
-        <v>12.97151660309227</v>
+        <v>12.93700303798219</v>
       </c>
       <c r="G7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I7" t="n">
         <v>122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7454</v>
+        <v>0.7614</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2757</v>
+        <v>0.2995</v>
       </c>
       <c r="L7" t="n">
-        <v>0.122</v>
+        <v>0.1298</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0643</v>
+        <v>0.0698</v>
       </c>
       <c r="N7" t="n">
         <v>11.11131222666323</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>+1455</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="O7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>+1333</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>2.667802721305943</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-1.15152392851577</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>-1.209564556068692</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.4645636922651887</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>5.503780025970594</v>
       </c>
     </row>
@@ -3463,53 +3587,56 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>99.7306</v>
+        <v>98.277</v>
       </c>
       <c r="F8" t="n">
-        <v>13.17505149280958</v>
+        <v>13.23753731777267</v>
       </c>
       <c r="G8" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I8" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6584</v>
+        <v>0.6159</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1816</v>
+        <v>0.1653</v>
       </c>
       <c r="L8" t="n">
-        <v>0.096</v>
+        <v>0.0843</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0518</v>
+        <v>0.0461</v>
       </c>
       <c r="N8" t="n">
         <v>11.95676267158673</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>+1831</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
+      <c r="O8" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>+2069</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
         <v>7.960442314835571</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>-0.6143076227322427</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-2.625967773270229</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>0.6652756946150876</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>0.4583275447545321</v>
       </c>
     </row>
@@ -3519,24 +3646,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ottawa Senators</t>
+          <t>Washington Capitals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>97.5943</v>
+        <v>97.5493</v>
       </c>
       <c r="F9" t="n">
-        <v>13.18758881524125</v>
+        <v>13.03764424759138</v>
       </c>
       <c r="G9" t="n">
         <v>76</v>
@@ -3548,39 +3675,42 @@
         <v>119</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5944</v>
+        <v>0.5994</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1382</v>
+        <v>0.1646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.074</v>
+        <v>0.079</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0356</v>
+        <v>0.0386</v>
       </c>
       <c r="N9" t="n">
-        <v>7.085134171727478</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>+2709</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>6.885314070682345</v>
+        <v>8.112523146305424</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>+2491</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>0.9021365557568833</v>
+        <v>2.255560444274506</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1603953307198461</v>
+        <v>-0.1653931253494979</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1043982595702159</v>
+        <v>-0.2190722107556898</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.774294866636687</v>
+        <v>-0.1833281609572859</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.6926801356603555</v>
       </c>
     </row>
     <row r="10">
@@ -3589,68 +3719,71 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Buffalo Sabres</t>
+          <t>Utah Mammoth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>97.309</v>
+        <v>97.1251</v>
       </c>
       <c r="F10" t="n">
-        <v>13.10730708993709</v>
+        <v>13.13898448440092</v>
       </c>
       <c r="G10" t="n">
         <v>75</v>
       </c>
       <c r="H10" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I10" t="n">
         <v>118</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5946</v>
+        <v>0.6103</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1332</v>
+        <v>0.1362</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0767</v>
+        <v>0.0769</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0403</v>
+        <v>0.0377</v>
       </c>
       <c r="N10" t="n">
-        <v>7.27216984942758</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>+2381</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>2.688928822630481</v>
+        <v>8.023130703542428</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>+2553</t>
+        </is>
       </c>
       <c r="Q10" t="n">
-        <v>-0.813418606700837</v>
+        <v>1.089305648752632</v>
       </c>
       <c r="R10" t="n">
-        <v>1.808448571737201</v>
+        <v>-0.7138021567542163</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4843569561060208</v>
+        <v>-0.2585590010263427</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3413878925229306</v>
+        <v>-0.0002497986944074219</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.201593091554644</v>
       </c>
     </row>
     <row r="11">
@@ -3659,24 +3792,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Minnesota Wild</t>
+          <t>Ottawa Senators</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OTT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>96.58540000000001</v>
+        <v>96.7248</v>
       </c>
       <c r="F11" t="n">
-        <v>13.21060781553542</v>
+        <v>13.23570864586917</v>
       </c>
       <c r="G11" t="n">
         <v>75</v>
@@ -3688,39 +3821,42 @@
         <v>118</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5989</v>
+        <v>0.5724</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1233</v>
+        <v>0.1328</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0675</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.032</v>
+        <v>0.036</v>
       </c>
       <c r="N11" t="n">
-        <v>8.309178835527998</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>+3025</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>4.548084092335117</v>
+        <v>7.085134171727478</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>+2678</t>
+        </is>
       </c>
       <c r="Q11" t="n">
-        <v>0.9717311497682485</v>
+        <v>6.885314070682345</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.228690474264837</v>
+        <v>0.9021365557568833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3214716825614959</v>
+        <v>-0.1603953307198461</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5739491403600642</v>
+        <v>-0.1043982595702159</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-3.774294866636687</v>
       </c>
     </row>
     <row r="12">
@@ -3729,24 +3865,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Utah Mammoth</t>
+          <t>Buffalo Sabres</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>96.2804</v>
+        <v>96.5192</v>
       </c>
       <c r="F12" t="n">
-        <v>13.15342073712039</v>
+        <v>13.13944808085891</v>
       </c>
       <c r="G12" t="n">
         <v>75</v>
@@ -3758,39 +3894,42 @@
         <v>118</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5937</v>
+        <v>0.5725</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1199</v>
+        <v>0.1298</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0707</v>
+        <v>0.0736</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0344</v>
+        <v>0.038</v>
       </c>
       <c r="N12" t="n">
-        <v>8.023130703542428</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>+2807</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1.089305648752632</v>
+        <v>7.27216984942758</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>+2532</t>
+        </is>
       </c>
       <c r="Q12" t="n">
-        <v>-0.7138021567542163</v>
+        <v>2.688928822630481</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.2585590010263427</v>
+        <v>-0.813418606700837</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0002497986944074219</v>
+        <v>1.808448571737201</v>
       </c>
       <c r="T12" t="n">
-        <v>2.201593091554644</v>
+        <v>0.4843569561060208</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3413878925229306</v>
       </c>
     </row>
     <row r="13">
@@ -3799,27 +3938,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pittsburgh Penguins</t>
+          <t>Minnesota Wild</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>95.6319</v>
+        <v>95.8605</v>
       </c>
       <c r="F13" t="n">
-        <v>13.11709602811617</v>
+        <v>13.24892422611417</v>
       </c>
       <c r="G13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13" t="n">
         <v>96</v>
@@ -3828,39 +3967,42 @@
         <v>117</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5512</v>
+        <v>0.5707</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1356</v>
+        <v>0.1148</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0689</v>
+        <v>0.0679</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0334</v>
+        <v>0.0317</v>
       </c>
       <c r="N13" t="n">
-        <v>9.661055316871911</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>+2894</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1.34269155366077</v>
+        <v>8.309178835527998</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>+3055</t>
+        </is>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1939456014570308</v>
+        <v>4.548084092335117</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.321621479320812</v>
+        <v>0.9717311497682485</v>
       </c>
       <c r="S13" t="n">
-        <v>1.122056776668267</v>
+        <v>-2.228690474264837</v>
       </c>
       <c r="T13" t="n">
-        <v>2.153989926052487</v>
+        <v>-0.3214716825614959</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.5739491403600642</v>
       </c>
     </row>
     <row r="14">
@@ -3869,24 +4011,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Washington Capitals</t>
+          <t>Boston Bruins</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>94.59820000000001</v>
+        <v>94.7894</v>
       </c>
       <c r="F14" t="n">
-        <v>13.15551836783152</v>
+        <v>13.21823436817418</v>
       </c>
       <c r="G14" t="n">
         <v>73</v>
@@ -3898,39 +4040,42 @@
         <v>116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5115</v>
+        <v>0.5178</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1206</v>
+        <v>0.1046</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0534</v>
+        <v>0.0553</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0249</v>
+        <v>0.0284</v>
       </c>
       <c r="N14" t="n">
-        <v>8.112523146305424</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>+3916</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>2.255560444274506</v>
+        <v>7.661371017102861</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>+3421</t>
+        </is>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1653931253494979</v>
+        <v>-2.291332495871128</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2190722107556898</v>
+        <v>2.033641962547492</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1833281609572859</v>
+        <v>-0.5129210599185793</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6926801356603555</v>
+        <v>-0.3496737315565279</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.975429322628814</v>
       </c>
     </row>
     <row r="15">
@@ -3939,68 +4084,71 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boston Bruins</t>
+          <t>Philadelphia Flyers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>94.57859999999999</v>
+        <v>93.48220000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>13.22494279576268</v>
+        <v>13.34251420941881</v>
       </c>
       <c r="G15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5052</v>
+        <v>0.4835</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0946</v>
+        <v>0.1052</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0542</v>
+        <v>0.052</v>
       </c>
       <c r="M15" t="n">
-        <v>0.026</v>
+        <v>0.0243</v>
       </c>
       <c r="N15" t="n">
-        <v>7.661371017102861</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>+3746</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>-2.291332495871128</v>
+        <v>6.130068512120818</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>+4015</t>
+        </is>
       </c>
       <c r="Q15" t="n">
-        <v>2.033641962547492</v>
+        <v>0.6891768331326394</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.5129210599185793</v>
+        <v>-1.777050617873852</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3496737315565279</v>
+        <v>1.213865842801857</v>
       </c>
       <c r="T15" t="n">
-        <v>1.975429322628814</v>
+        <v>-0.1347387413776844</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.6900098742082689</v>
       </c>
     </row>
     <row r="16">
@@ -4023,13 +4171,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>94.0806</v>
+        <v>93.4166</v>
       </c>
       <c r="F16" t="n">
-        <v>13.10901553393034</v>
+        <v>13.14161765733067</v>
       </c>
       <c r="G16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H16" t="n">
         <v>94</v>
@@ -4038,38 +4186,41 @@
         <v>115</v>
       </c>
       <c r="J16" t="n">
-        <v>0.501</v>
+        <v>0.4792</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1081</v>
+        <v>0.098</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0525</v>
+        <v>0.0506</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0263</v>
+        <v>0.0248</v>
       </c>
       <c r="N16" t="n">
         <v>7.139596880634292</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>+3702</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
+      <c r="O16" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>+3932</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
         <v>0.0935484444468655</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>0.7861377851463477</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.6626621109892172</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.02152261001538667</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-1.011178859315558</v>
       </c>
     </row>
@@ -4079,68 +4230,71 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anaheim Ducks</t>
+          <t>Pittsburgh Penguins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93.8887</v>
+        <v>93.17570000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>13.08785091197747</v>
+        <v>13.18317902218251</v>
       </c>
       <c r="G17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I17" t="n">
         <v>115</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5465</v>
+        <v>0.4703</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1277</v>
+        <v>0.0941</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0571</v>
+        <v>0.0511</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0254</v>
+        <v>0.023</v>
       </c>
       <c r="N17" t="n">
-        <v>6.925373482467831</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>+3837</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>-1.010932889478177</v>
+        <v>9.661055316871911</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>+4248</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>-0.6363337953433582</v>
+        <v>1.34269155366077</v>
       </c>
       <c r="R17" t="n">
-        <v>2.544592005696049</v>
+        <v>-0.1939456014570308</v>
       </c>
       <c r="S17" t="n">
-        <v>0.03952564658535663</v>
+        <v>-2.321621479320812</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7237187600067777</v>
+        <v>1.122056776668267</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.153989926052487</v>
       </c>
     </row>
     <row r="18">
@@ -4149,12 +4303,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philadelphia Flyers</t>
+          <t>New York Rangers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4163,10 +4317,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>92.8844</v>
+        <v>92.8002</v>
       </c>
       <c r="F18" t="n">
-        <v>13.34853755980402</v>
+        <v>13.18224021574901</v>
       </c>
       <c r="G18" t="n">
         <v>71</v>
@@ -4175,42 +4329,45 @@
         <v>93</v>
       </c>
       <c r="I18" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4617</v>
+        <v>0.4634</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0961</v>
+        <v>0.0931</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0502</v>
+        <v>0.0417</v>
       </c>
       <c r="M18" t="n">
-        <v>0.023</v>
+        <v>0.0188</v>
       </c>
       <c r="N18" t="n">
-        <v>6.130068512120818</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>+4248</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>0.6891768331326394</v>
+        <v>7.823147646950697</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>+5219</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>-1.777050617873852</v>
+        <v>-3.89011573995344</v>
       </c>
       <c r="R18" t="n">
-        <v>1.213865842801857</v>
+        <v>-1.099307448315102</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1347387413776844</v>
+        <v>1.062183023009203</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6900098742082689</v>
+        <v>-0.3068551321166658</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.812518268983693</v>
       </c>
     </row>
     <row r="19">
@@ -4219,68 +4376,71 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>San Jose Sharks</t>
+          <t>St. Louis Blues</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>92.28100000000001</v>
+        <v>92.3235</v>
       </c>
       <c r="F19" t="n">
-        <v>13.19406864256566</v>
+        <v>13.1662364678853</v>
       </c>
       <c r="G19" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I19" t="n">
         <v>114</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5007</v>
+        <v>0.4647</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1064</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0473</v>
+        <v>0.0429</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0195</v>
+        <v>0.0187</v>
       </c>
       <c r="N19" t="n">
-        <v>7.118157267955309</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>+5028</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>-6.895844258138982</v>
+        <v>6.73886642624792</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>+5248</t>
+        </is>
       </c>
       <c r="Q19" t="n">
-        <v>0.3774784671534505</v>
+        <v>-2.460739273116321</v>
       </c>
       <c r="R19" t="n">
-        <v>2.764600425281233</v>
+        <v>0.7180021331477906</v>
       </c>
       <c r="S19" t="n">
-        <v>1.216698428759594</v>
+        <v>1.897311008724077</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9808322764299869</v>
+        <v>-0.8762541507096491</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.379692298778255</v>
       </c>
     </row>
     <row r="20">
@@ -4289,24 +4449,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Detroit Red Wings</t>
+          <t>Anaheim Ducks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>91.8823</v>
+        <v>91.88809999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>13.15950470064875</v>
+        <v>13.10792737872836</v>
       </c>
       <c r="G20" t="n">
         <v>70</v>
@@ -4315,42 +4475,45 @@
         <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4208</v>
+        <v>0.4838</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0687</v>
+        <v>0.0999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0354</v>
+        <v>0.046</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0149</v>
+        <v>0.0207</v>
       </c>
       <c r="N20" t="n">
-        <v>7.181298352106282</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>+6611</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>-0.6291308431913376</v>
+        <v>6.925373482467831</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>+4731</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>-2.442251294568766</v>
+        <v>-1.010932889478177</v>
       </c>
       <c r="R20" t="n">
-        <v>0.811402061902921</v>
+        <v>-0.6363337953433582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.247443698897508</v>
+        <v>2.544592005696049</v>
       </c>
       <c r="T20" t="n">
-        <v>1.259161851603387</v>
+        <v>0.03952564658535663</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.7237187600067777</v>
       </c>
     </row>
     <row r="21">
@@ -4359,12 +4522,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>St. Louis Blues</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NSH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4373,10 +4536,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>91.5359</v>
+        <v>91.7821</v>
       </c>
       <c r="F21" t="n">
-        <v>13.14742547686303</v>
+        <v>13.19795583390926</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -4385,42 +4548,45 @@
         <v>92</v>
       </c>
       <c r="I21" t="n">
-        <v>113</v>
+        <v>113.0499999999993</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4464</v>
+        <v>0.4463</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0603</v>
+        <v>0.065</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>0.0444</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0177</v>
+        <v>0.018</v>
       </c>
       <c r="N21" t="n">
-        <v>6.73886642624792</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>+5550</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>-2.460739273116321</v>
+        <v>8.467264727101742</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>+5456</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>0.7180021331477906</v>
+        <v>-3.532544672320494</v>
       </c>
       <c r="R21" t="n">
-        <v>1.897311008724077</v>
+        <v>2.679875306851186</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8762541507096491</v>
+        <v>-1.077626789194386</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.379692298778255</v>
+        <v>0.06166121207429784</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.565931389377716</v>
       </c>
     </row>
     <row r="22">
@@ -4429,12 +4595,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New York Rangers</t>
+          <t>New Jersey Devils</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>NJD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4443,54 +4609,57 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90.8215</v>
+        <v>91.44110000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>13.20701632762025</v>
+        <v>13.23716181948772</v>
       </c>
       <c r="G22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" t="n">
         <v>91</v>
       </c>
       <c r="I22" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4038</v>
+        <v>0.4168</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0795</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0347</v>
+        <v>0.0385</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0145</v>
+        <v>0.0174</v>
       </c>
       <c r="N22" t="n">
-        <v>7.823147646950697</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>+6797</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>-3.89011573995344</v>
+        <v>8.08185262922734</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>+5647</t>
+        </is>
       </c>
       <c r="Q22" t="n">
-        <v>-1.099307448315102</v>
+        <v>0.2320042060015959</v>
       </c>
       <c r="R22" t="n">
-        <v>1.062183023009203</v>
+        <v>-1.91772232781308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3068551321166658</v>
+        <v>0.6511324305591233</v>
       </c>
       <c r="T22" t="n">
-        <v>1.812518268983693</v>
+        <v>0.5227212781263088</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-1.701319430516024</v>
       </c>
     </row>
     <row r="23">
@@ -4499,24 +4668,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Winnipeg Jets</t>
+          <t>San Jose Sharks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WPG</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.7805</v>
+        <v>91.226</v>
       </c>
       <c r="F23" t="n">
-        <v>13.34267298715831</v>
+        <v>13.19314708145829</v>
       </c>
       <c r="G23" t="n">
         <v>69</v>
@@ -4528,39 +4697,42 @@
         <v>113</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4274</v>
+        <v>0.4671</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0592</v>
+        <v>0.0935</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0325</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>0.013</v>
+        <v>0.0169</v>
       </c>
       <c r="N23" t="n">
-        <v>8.140000216729245</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>+7592</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>-2.258624678906664</v>
+        <v>7.118157267955309</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>+5817</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>0.9224232177474913</v>
+        <v>-6.895844258138982</v>
       </c>
       <c r="R23" t="n">
-        <v>-2.091474010424004</v>
+        <v>0.3774784671534505</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5800098854014704</v>
+        <v>2.764600425281233</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01344050617781949</v>
+        <v>1.216698428759594</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.9808322764299869</v>
       </c>
     </row>
     <row r="24">
@@ -4569,24 +4741,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Jersey Devils</t>
+          <t>Los Angeles Kings</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>LAK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>90.72790000000001</v>
+        <v>91.02200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>13.26942611256929</v>
+        <v>13.23466779496804</v>
       </c>
       <c r="G24" t="n">
         <v>69</v>
@@ -4595,42 +4767,45 @@
         <v>91</v>
       </c>
       <c r="I24" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3996</v>
+        <v>0.4618</v>
       </c>
       <c r="K24" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0331</v>
+        <v>0.0404</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0142</v>
+        <v>0.0164</v>
       </c>
       <c r="N24" t="n">
-        <v>8.08185262922734</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>+6942</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>0.2320042060015959</v>
+        <v>8.389923070792923</v>
+      </c>
+      <c r="O24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>+5998</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>-1.91772232781308</v>
+        <v>-0.4678380579662646</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6511324305591233</v>
+        <v>-1.369875589206126</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5227212781263088</v>
+        <v>-1.807153891127034</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.701319430516024</v>
+        <v>-0.756047318569063</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4588287284272445</v>
       </c>
     </row>
     <row r="25">
@@ -4639,12 +4814,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Winnipeg Jets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NSH</t>
+          <t>WPG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4653,54 +4828,57 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>89.98350000000001</v>
+        <v>90.5626</v>
       </c>
       <c r="F25" t="n">
-        <v>13.24425795531326</v>
+        <v>13.33228623401187</v>
       </c>
       <c r="G25" t="n">
         <v>68</v>
       </c>
       <c r="H25" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I25" t="n">
         <v>112</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3947</v>
+        <v>0.4117</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0517</v>
+        <v>0.058</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0342</v>
+        <v>0.0351</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0141</v>
+        <v>0.0138</v>
       </c>
       <c r="N25" t="n">
-        <v>8.467264727101742</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>+6992</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>-3.532544672320494</v>
+        <v>8.140000216729245</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>+7146</t>
+        </is>
       </c>
       <c r="Q25" t="n">
-        <v>2.679875306851186</v>
+        <v>-2.258624678906664</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.077626789194386</v>
+        <v>0.9224232177474913</v>
       </c>
       <c r="S25" t="n">
-        <v>0.06166121207429784</v>
+        <v>-2.091474010424004</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.565931389377716</v>
+        <v>0.5800098854014704</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.01344050617781949</v>
       </c>
     </row>
     <row r="26">
@@ -4709,68 +4887,71 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Los Angeles Kings</t>
+          <t>Detroit Red Wings</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LAK</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>88.55370000000001</v>
+        <v>89.8188</v>
       </c>
       <c r="F26" t="n">
-        <v>13.22976261963521</v>
+        <v>13.20624878838446</v>
       </c>
       <c r="G26" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H26" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I26" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3848</v>
+        <v>0.3668</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0645</v>
+        <v>0.0577</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0285</v>
+        <v>0.0298</v>
       </c>
       <c r="M26" t="n">
-        <v>0.012</v>
+        <v>0.0121</v>
       </c>
       <c r="N26" t="n">
-        <v>8.389923070792923</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>+8233</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>-0.4678380579662646</v>
+        <v>7.181298352106282</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>+8164</t>
+        </is>
       </c>
       <c r="Q26" t="n">
-        <v>-1.369875589206126</v>
+        <v>-0.6291308431913376</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.807153891127034</v>
+        <v>-2.442251294568766</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.756047318569063</v>
+        <v>0.811402061902921</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4588287284272445</v>
+        <v>-0.247443698897508</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.259161851603387</v>
       </c>
     </row>
     <row r="27">
@@ -4779,68 +4960,71 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Seattle Kraken</t>
+          <t>Toronto Maple Leafs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86.6865</v>
+        <v>89.3245</v>
       </c>
       <c r="F27" t="n">
-        <v>13.15431189162452</v>
+        <v>13.22572083930294</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H27" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I27" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3306</v>
+        <v>0.3481</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0496</v>
+        <v>0.0499</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0189</v>
+        <v>0.0286</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0065</v>
+        <v>0.0138</v>
       </c>
       <c r="N27" t="n">
-        <v>5.794809968760188</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>+15285</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>-6.785736079272034</v>
+        <v>8.7101896414871</v>
+      </c>
+      <c r="O27" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>+7146</t>
+        </is>
       </c>
       <c r="Q27" t="n">
-        <v>-0.5896294940300654</v>
+        <v>-6.764227944005042</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02230285830604234</v>
+        <v>2.421496712991583</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.809151658761522</v>
+        <v>-1.734590603700175</v>
       </c>
       <c r="T27" t="n">
-        <v>1.654131583090938</v>
+        <v>-0.4177791933109138</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.2944937391059024</v>
       </c>
     </row>
     <row r="28">
@@ -4849,68 +5033,71 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Seattle Kraken</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>86.31780000000001</v>
+        <v>86.60039999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>13.38923934856022</v>
+        <v>13.14965441299193</v>
       </c>
       <c r="G28" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H28" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I28" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2678</v>
+        <v>0.3246</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0305</v>
+        <v>0.0484</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0175</v>
+        <v>0.0197</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0067</v>
+        <v>0.0072</v>
       </c>
       <c r="N28" t="n">
-        <v>9.184839315742089</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>+14825</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>0.6345831753595271</v>
+        <v>5.794809968760188</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>+13789</t>
+        </is>
       </c>
       <c r="Q28" t="n">
-        <v>-1.389234379191214</v>
+        <v>-6.785736079272034</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.815739636602882</v>
+        <v>-0.5896294940300654</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.3021413685913394</v>
+        <v>0.02230285830604234</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.251631231823174</v>
+        <v>-0.809151658761522</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.654131583090938</v>
       </c>
     </row>
     <row r="29">
@@ -4919,12 +5106,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Toronto Maple Leafs</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4933,10 +5120,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>86.2591</v>
+        <v>86.27070000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>13.23678542693973</v>
+        <v>13.41181602882023</v>
       </c>
       <c r="G29" t="n">
         <v>64</v>
@@ -4948,39 +5135,42 @@
         <v>108</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2661</v>
+        <v>0.2736</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0276</v>
+        <v>0.0345</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0169</v>
+        <v>0.017</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0074</v>
+        <v>0.008</v>
       </c>
       <c r="N29" t="n">
-        <v>8.7101896414871</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>+13414</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>-6.764227944005042</v>
+        <v>9.184839315742089</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>+12400</t>
+        </is>
       </c>
       <c r="Q29" t="n">
-        <v>2.421496712991583</v>
+        <v>0.6345831753595271</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.734590603700175</v>
+        <v>-1.389234379191214</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.4177791933109138</v>
+        <v>-1.815739636602882</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2944937391059024</v>
+        <v>-0.3021413685913394</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-3.251631231823174</v>
       </c>
     </row>
     <row r="30">
@@ -4989,24 +5179,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New York Islanders</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NYI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>86.1195</v>
+        <v>85.54130000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>13.24397825602279</v>
+        <v>13.08356267502193</v>
       </c>
       <c r="G30" t="n">
         <v>64</v>
@@ -5015,42 +5205,45 @@
         <v>86</v>
       </c>
       <c r="I30" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2715</v>
+        <v>0.2734</v>
       </c>
       <c r="K30" t="n">
-        <v>0.037</v>
+        <v>0.0244</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0169</v>
+        <v>0.0163</v>
       </c>
       <c r="M30" t="n">
-        <v>0.007</v>
+        <v>0.0063</v>
       </c>
       <c r="N30" t="n">
-        <v>5.904979974439156</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>+14186</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>-3.104081129551034</v>
+        <v>6.748602304917045</v>
+      </c>
+      <c r="O30" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>+15773</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>0.4793389366472667</v>
+        <v>-11.92318674235645</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.835774924911927</v>
+        <v>-0.4668780224584904</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.3842797473246679</v>
+        <v>4.677470041626046</v>
       </c>
       <c r="T30" t="n">
-        <v>-2.610162037482091</v>
+        <v>0.1662788500620234</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-1.580629202394376</v>
       </c>
     </row>
     <row r="31">
@@ -5059,68 +5252,71 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>New York Islanders</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NYI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>82.98739999999999</v>
+        <v>84.6494</v>
       </c>
       <c r="F31" t="n">
-        <v>12.98953093962223</v>
+        <v>13.23953202197178</v>
       </c>
       <c r="G31" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H31" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I31" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2173</v>
+        <v>0.2418</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0164</v>
+        <v>0.0297</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0132</v>
+        <v>0.0147</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0048</v>
+        <v>0.0064</v>
       </c>
       <c r="N31" t="n">
-        <v>6.748602304917045</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>+20733</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>-11.92318674235645</v>
+        <v>5.904979974439156</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>+15525</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>-0.4668780224584904</v>
+        <v>-3.104081129551034</v>
       </c>
       <c r="R31" t="n">
-        <v>4.677470041626046</v>
+        <v>0.4793389366472667</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1662788500620234</v>
+        <v>-0.835774924911927</v>
       </c>
       <c r="T31" t="n">
-        <v>-1.580629202394376</v>
+        <v>-0.3842797473246679</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-2.610162037482091</v>
       </c>
     </row>
     <row r="32">
@@ -5143,53 +5339,56 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>82.8302</v>
+        <v>81.4348</v>
       </c>
       <c r="F32" t="n">
-        <v>13.13238797482743</v>
+        <v>13.07656103892994</v>
       </c>
       <c r="G32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I32" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2318</v>
+        <v>0.197</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0276</v>
+        <v>0.0224</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0118</v>
+        <v>0.0101</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0037</v>
+        <v>0.0034</v>
       </c>
       <c r="N32" t="n">
         <v>5.049701439462</v>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>+26927</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
+      <c r="O32" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>+29312</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
         <v>-11.04585406916108</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>0.3170507282545384</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>2.846671419738107</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-0.6861403554068117</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>-1.128093930872227</v>
       </c>
     </row>
@@ -5213,53 +5412,56 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>81.5594</v>
+        <v>81.39019999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>12.9709250298355</v>
+        <v>12.97687111280635</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
       </c>
       <c r="H33" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I33" t="n">
         <v>103</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2004</v>
+        <v>0.2002</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0215</v>
+        <v>0.0223</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0104</v>
+        <v>0.0097</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0037</v>
+        <v>0.0039</v>
       </c>
       <c r="N33" t="n">
         <v>4.091492155309823</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>+26927</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
+      <c r="O33" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>+25541</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
         <v>-6.307966720721302</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>0.09396063956343431</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>0.5578714034863962</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>0.1134326182738392</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>-5.427594747348694</v>
       </c>
     </row>

--- a/output/nhl_2026_27_projections_v3.xlsx
+++ b/output/nhl_2026_27_projections_v3.xlsx
@@ -678,24 +678,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carolina Hurricanes</t>
+          <t>Colorado Avalanche</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>107.6031</v>
+        <v>107.5517</v>
       </c>
       <c r="F2" t="n">
-        <v>12.63599371730306</v>
+        <v>12.69404746304737</v>
       </c>
       <c r="G2" t="n">
         <v>86</v>
@@ -707,42 +707,42 @@
         <v>128</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8436</v>
+        <v>0.8724</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4137</v>
+        <v>0.3469</v>
       </c>
       <c r="L2" t="n">
-        <v>0.192</v>
+        <v>0.1866</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1132</v>
+        <v>0.1023</v>
       </c>
       <c r="N2" t="n">
-        <v>8.287039933520225</v>
+        <v>10.43058285193634</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8</v>
+        <v>-6.5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>+783</t>
+          <t>+878</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>14.86116182018452</v>
+        <v>14.53741765167042</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1669627848400201</v>
+        <v>-1.301203426971305</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2526154518856217</v>
+        <v>-1.546832861222726</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2384111455252166</v>
+        <v>0.9853425117174447</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.298489907419239</v>
+        <v>1.035664354688619</v>
       </c>
     </row>
     <row r="3">
@@ -751,24 +751,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colorado Avalanche</t>
+          <t>Carolina Hurricanes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>107.416</v>
+        <v>107.5266</v>
       </c>
       <c r="F3" t="n">
-        <v>12.75622264314998</v>
+        <v>12.5644211529179</v>
       </c>
       <c r="G3" t="n">
         <v>86</v>
@@ -780,42 +780,42 @@
         <v>128</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8702</v>
+        <v>0.8454</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3424</v>
+        <v>0.4146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1886</v>
+        <v>0.1933</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1036</v>
+        <v>0.1129</v>
       </c>
       <c r="N3" t="n">
-        <v>10.43058285193634</v>
+        <v>8.287039933520225</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.5</v>
+        <v>-1.8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>+865</t>
+          <t>+786</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>14.53741765167042</v>
+        <v>14.86116182018452</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.301203426971305</v>
+        <v>-0.1669627848400201</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.546832861222726</v>
+        <v>-0.2526154518856217</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9853425117174447</v>
+        <v>0.2384111455252166</v>
       </c>
       <c r="U3" t="n">
-        <v>1.035664354688619</v>
+        <v>-1.298489907419239</v>
       </c>
     </row>
     <row r="4">
@@ -838,31 +838,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105.0989</v>
+        <v>105.2254</v>
       </c>
       <c r="F4" t="n">
-        <v>12.80805697295036</v>
+        <v>12.73178717543095</v>
       </c>
       <c r="G4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I4" t="n">
         <v>125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8547</v>
+        <v>0.8583</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4173</v>
+        <v>0.4208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1711</v>
+        <v>0.1691</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0896</v>
+        <v>0.0895</v>
       </c>
       <c r="N4" t="n">
         <v>9.436252802325914</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>+1016</t>
+          <t>+1017</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>104.481</v>
+        <v>104.6473</v>
       </c>
       <c r="F5" t="n">
-        <v>12.80072751301606</v>
+        <v>12.77810747775551</v>
       </c>
       <c r="G5" t="n">
         <v>83</v>
@@ -926,16 +926,16 @@
         <v>125</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8128</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2499</v>
+        <v>0.2534</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1513</v>
+        <v>0.1509</v>
       </c>
       <c r="M5" t="n">
-        <v>0.079</v>
+        <v>0.0781</v>
       </c>
       <c r="N5" t="n">
         <v>9.85275482151591</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>+1166</t>
+          <t>+1180</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -970,12 +970,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tampa Bay Lightning</t>
+          <t>Montreal Canadiens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TBL</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -984,57 +984,57 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102.882</v>
+        <v>103.2097</v>
       </c>
       <c r="F6" t="n">
-        <v>13.08393652306117</v>
+        <v>12.67461993548725</v>
       </c>
       <c r="G6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2399</v>
+        <v>0.2383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1235</v>
+        <v>0.1173</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0677</v>
+        <v>0.0592</v>
       </c>
       <c r="N6" t="n">
-        <v>11.95676267158673</v>
+        <v>8.510549067215697</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.7</v>
+        <v>-2.5</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>+1377</t>
+          <t>+1589</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>9.436735107173774</v>
+        <v>1.740788541281878</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.8022613128825858</v>
+        <v>2.510899193633914</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8994067827698127</v>
+        <v>2.196737059056645</v>
       </c>
       <c r="T6" t="n">
-        <v>2.111485424037829</v>
+        <v>0.6120765889048018</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5100934026557666</v>
+        <v>1.804633765882705</v>
       </c>
     </row>
     <row r="7">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Montreal Canadiens</t>
+          <t>Tampa Bay Lightning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>TBL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102.2868</v>
+        <v>102.8115</v>
       </c>
       <c r="F7" t="n">
-        <v>12.77859440656525</v>
+        <v>13.02534965839199</v>
       </c>
       <c r="G7" t="n">
         <v>81</v>
@@ -1069,45 +1069,45 @@
         <v>103</v>
       </c>
       <c r="I7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7165</v>
+        <v>0.7295</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2122</v>
+        <v>0.2388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1138</v>
+        <v>0.1247</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0613</v>
+        <v>0.0692</v>
       </c>
       <c r="N7" t="n">
-        <v>8.510549067215697</v>
+        <v>11.95676267158673</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.5</v>
+        <v>-6.7</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>+1531</t>
+          <t>+1345</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1.740788541281878</v>
+        <v>9.436735107173774</v>
       </c>
       <c r="R7" t="n">
-        <v>2.510899193633914</v>
+        <v>-0.8022613128825858</v>
       </c>
       <c r="S7" t="n">
-        <v>2.196737059056645</v>
+        <v>-0.8994067827698127</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6120765889048018</v>
+        <v>2.111485424037829</v>
       </c>
       <c r="U7" t="n">
-        <v>1.804633765882705</v>
+        <v>0.5100934026557666</v>
       </c>
     </row>
     <row r="8">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ottawa Senators</t>
+          <t>Edmonton Oilers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.9931</v>
+        <v>101.6318</v>
       </c>
       <c r="F8" t="n">
-        <v>12.77485702805353</v>
+        <v>12.96984388668748</v>
       </c>
       <c r="G8" t="n">
         <v>80</v>
@@ -1145,42 +1145,42 @@
         <v>123</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7091</v>
+        <v>0.783</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2076</v>
+        <v>0.2956</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1091</v>
+        <v>0.1245</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0544</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.085134171727478</v>
+        <v>11.11131222666323</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.1</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>+1738</t>
+          <t>+1470</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>8.451268172646309</v>
+        <v>3.210989299173198</v>
       </c>
       <c r="R8" t="n">
-        <v>1.77019449892022</v>
+        <v>-1.056838272229703</v>
       </c>
       <c r="S8" t="n">
-        <v>1.156408289279054</v>
+        <v>-0.8014174971800627</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3775057526043846</v>
+        <v>1.235756684107004</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.897413578334854</v>
+        <v>3.501549285384193</v>
       </c>
     </row>
     <row r="9">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edmonton Oilers</t>
+          <t>Ottawa Senators</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>OTT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101.821</v>
+        <v>101.283</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03574133124793</v>
+        <v>12.75202620830281</v>
       </c>
       <c r="G9" t="n">
         <v>80</v>
@@ -1215,45 +1215,45 @@
         <v>102</v>
       </c>
       <c r="I9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7891</v>
+        <v>0.6962</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3019</v>
+        <v>0.1967</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1269</v>
+        <v>0.107</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0644</v>
+        <v>0.0549</v>
       </c>
       <c r="N9" t="n">
-        <v>11.11131222666323</v>
+        <v>7.085134171727478</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>-4.1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>+1453</t>
+          <t>+1721</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3.210989299173198</v>
+        <v>8.451268172646309</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.056838272229703</v>
+        <v>1.77019449892022</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8014174971800627</v>
+        <v>1.156408289279054</v>
       </c>
       <c r="T9" t="n">
-        <v>1.235756684107004</v>
+        <v>0.3775057526043846</v>
       </c>
       <c r="U9" t="n">
-        <v>3.501549285384193</v>
+        <v>-2.897413578334854</v>
       </c>
     </row>
     <row r="10">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100.1821</v>
+        <v>100.2607</v>
       </c>
       <c r="F10" t="n">
-        <v>13.00620835353538</v>
+        <v>12.96781986091704</v>
       </c>
       <c r="G10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="n">
         <v>101</v>
@@ -1291,16 +1291,16 @@
         <v>121</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6656</v>
+        <v>0.6708</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1955</v>
+        <v>0.1928</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0917</v>
+        <v>0.0911</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0486</v>
+        <v>0.0472</v>
       </c>
       <c r="N10" t="n">
         <v>8.112523146305424</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>+1958</t>
+          <t>+2019</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>99.093</v>
+        <v>98.7401</v>
       </c>
       <c r="F11" t="n">
-        <v>13.06614034067981</v>
+        <v>13.04902983780675</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
@@ -1364,16 +1364,16 @@
         <v>120</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6806</v>
+        <v>0.6701</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1402</v>
+        <v>0.1357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0851</v>
+        <v>0.0881</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0386</v>
+        <v>0.0402</v>
       </c>
       <c r="N11" t="n">
         <v>8.309178835527998</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>+2491</t>
+          <t>+2388</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>97.38849999999999</v>
+        <v>96.9571</v>
       </c>
       <c r="F12" t="n">
-        <v>13.09418624891796</v>
+        <v>13.10187106838368</v>
       </c>
       <c r="G12" t="n">
         <v>76</v>
@@ -1434,19 +1434,19 @@
         <v>97</v>
       </c>
       <c r="I12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5673</v>
+        <v>0.5589</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1276</v>
+        <v>0.1232</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0649</v>
+        <v>0.0646</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0329</v>
+        <v>0.0346</v>
       </c>
       <c r="N12" t="n">
         <v>7.27216984942758</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>+2940</t>
+          <t>+2790</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>97.0558</v>
+        <v>96.8592</v>
       </c>
       <c r="F13" t="n">
-        <v>13.07049234485885</v>
+        <v>13.04591870891031</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -1510,16 +1510,16 @@
         <v>118</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6249</v>
+        <v>0.6221</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1123</v>
+        <v>0.1066</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0665</v>
+        <v>0.0687</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03</v>
+        <v>0.0321</v>
       </c>
       <c r="N13" t="n">
         <v>8.023130703542428</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>+3233</t>
+          <t>+3015</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>95.0716</v>
+        <v>94.40779999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>13.21966525275657</v>
+        <v>13.11450716534247</v>
       </c>
       <c r="G14" t="n">
         <v>73</v>
@@ -1580,19 +1580,19 @@
         <v>95</v>
       </c>
       <c r="I14" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5041</v>
+        <v>0.488</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0954</v>
+        <v>0.0867</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0496</v>
+        <v>0.0482</v>
       </c>
       <c r="M14" t="n">
-        <v>0.023</v>
+        <v>0.0229</v>
       </c>
       <c r="N14" t="n">
         <v>7.661371017102861</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>+4248</t>
+          <t>+4267</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>93.74379999999999</v>
+        <v>93.71129999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>13.23280288779466</v>
+        <v>13.21520398902897</v>
       </c>
       <c r="G15" t="n">
         <v>72</v>
@@ -1656,16 +1656,16 @@
         <v>115</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4719</v>
+        <v>0.4801</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0927</v>
+        <v>0.0944</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0443</v>
+        <v>0.0434</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0202</v>
+        <v>0.0197</v>
       </c>
       <c r="N15" t="n">
         <v>6.130068512120818</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>+4850</t>
+          <t>+4976</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>93.7159</v>
+        <v>93.3905</v>
       </c>
       <c r="F16" t="n">
-        <v>13.07881847642492</v>
+        <v>13.01923806549295</v>
       </c>
       <c r="G16" t="n">
         <v>72</v>
@@ -1726,19 +1726,19 @@
         <v>94</v>
       </c>
       <c r="I16" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4774</v>
+        <v>0.4709</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="L16" t="n">
-        <v>0.044</v>
+        <v>0.0434</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0193</v>
+        <v>0.0184</v>
       </c>
       <c r="N16" t="n">
         <v>7.139596880634292</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>+5081</t>
+          <t>+5335</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>92.83580000000001</v>
+        <v>92.5158</v>
       </c>
       <c r="F17" t="n">
-        <v>13.22705310541185</v>
+        <v>13.19383030343378</v>
       </c>
       <c r="G17" t="n">
         <v>71</v>
@@ -1802,16 +1802,16 @@
         <v>114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4539</v>
+        <v>0.4445</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0813</v>
+        <v>0.0803</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0392</v>
+        <v>0.0388</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0199</v>
+        <v>0.0177</v>
       </c>
       <c r="N17" t="n">
         <v>9.661055316871911</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>+4925</t>
+          <t>+5550</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -1860,31 +1860,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91.96550000000001</v>
+        <v>92.41670000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>13.07311747021494</v>
+        <v>13.01610552393845</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18" t="n">
         <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4677</v>
+        <v>0.4747</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0559</v>
+        <v>0.0595</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0366</v>
+        <v>0.0355</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0133</v>
+        <v>0.014</v>
       </c>
       <c r="N18" t="n">
         <v>6.73886642624792</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>+7419</t>
+          <t>+7043</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>91.5638</v>
+        <v>91.6692</v>
       </c>
       <c r="F19" t="n">
-        <v>13.26660204547431</v>
+        <v>13.18906238125552</v>
       </c>
       <c r="G19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" t="n">
         <v>92</v>
@@ -1948,16 +1948,16 @@
         <v>114</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5052</v>
+        <v>0.5074</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1009</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0387</v>
+        <v>0.0389</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0163</v>
+        <v>0.0161</v>
       </c>
       <c r="N19" t="n">
         <v>8.389923070792923</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>+6035</t>
+          <t>+6111</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>91.4713</v>
+        <v>91.5787</v>
       </c>
       <c r="F20" t="n">
-        <v>13.24839342346197</v>
+        <v>13.17141430999316</v>
       </c>
       <c r="G20" t="n">
         <v>70</v>
@@ -2021,16 +2021,16 @@
         <v>113</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4593</v>
+        <v>0.4572</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0526</v>
+        <v>0.0527</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0365</v>
+        <v>0.037</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0171</v>
+        <v>0.0164</v>
       </c>
       <c r="N20" t="n">
         <v>8.467264727101742</v>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>+5748</t>
+          <t>+5998</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>90.82340000000001</v>
+        <v>90.9911</v>
       </c>
       <c r="F21" t="n">
-        <v>13.13901350207011</v>
+        <v>13.10347247446603</v>
       </c>
       <c r="G21" t="n">
         <v>69</v>
@@ -2094,16 +2094,16 @@
         <v>112</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3909</v>
+        <v>0.3969</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0577</v>
+        <v>0.0593</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0301</v>
+        <v>0.0295</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0128</v>
+        <v>0.0121</v>
       </c>
       <c r="N21" t="n">
         <v>8.08185262922734</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>+7712</t>
+          <t>+8164</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2138,71 +2138,71 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toronto Maple Leafs</t>
+          <t>New York Rangers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Metropolitan</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>89.83880000000001</v>
+        <v>89.48260000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>13.08096807321894</v>
+        <v>13.31862740013333</v>
       </c>
       <c r="G22" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H22" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I22" t="n">
         <v>111</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3466</v>
+        <v>0.3515</v>
       </c>
       <c r="K22" t="n">
-        <v>0.044</v>
+        <v>0.0532</v>
       </c>
       <c r="L22" t="n">
-        <v>0.025</v>
+        <v>0.0234</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0103</v>
+        <v>0.0092</v>
       </c>
       <c r="N22" t="n">
-        <v>8.7101896414871</v>
+        <v>7.823147646950697</v>
       </c>
       <c r="O22" t="n">
-        <v>13.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>+9609</t>
+          <t>+10770</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>-8.193380227493302</v>
+        <v>-4.799844584438726</v>
       </c>
       <c r="R22" t="n">
-        <v>2.580073488194848</v>
+        <v>-1.908540197038762</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7984428608114038</v>
+        <v>0.4458023315861614</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09756098771463831</v>
+        <v>-0.1363557253125856</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4100984906928617</v>
+        <v>0.8318037149568038</v>
       </c>
     </row>
     <row r="23">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Toronto Maple Leafs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2225,57 +2225,57 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.3768</v>
+        <v>89.1717</v>
       </c>
       <c r="F23" t="n">
-        <v>13.16504286340761</v>
+        <v>13.08918453476681</v>
       </c>
       <c r="G23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H23" t="n">
         <v>89</v>
       </c>
       <c r="I23" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J23" t="n">
-        <v>0.332</v>
+        <v>0.3325</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0463</v>
+        <v>0.0427</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0249</v>
+        <v>0.0238</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0102</v>
+        <v>0.01</v>
       </c>
       <c r="N23" t="n">
-        <v>9.184839315742089</v>
+        <v>8.7101896414871</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5</v>
+        <v>13.2</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>+9704</t>
+          <t>+9900</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>0.6979198033265082</v>
+        <v>-8.193380227493302</v>
       </c>
       <c r="R23" t="n">
-        <v>-2.218535999354475</v>
+        <v>2.580073488194848</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3343300754021691</v>
+        <v>-0.7984428608114038</v>
       </c>
       <c r="T23" t="n">
-        <v>1.285179068259477</v>
+        <v>0.09756098771463831</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.142967471019861</v>
+        <v>0.4100984906928617</v>
       </c>
     </row>
     <row r="24">
@@ -2284,71 +2284,71 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Winnipeg Jets</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WPG</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>89.19759999999999</v>
+        <v>88.7985</v>
       </c>
       <c r="F24" t="n">
-        <v>13.03733682372077</v>
+        <v>13.10401729535366</v>
       </c>
       <c r="G24" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H24" t="n">
         <v>89</v>
       </c>
       <c r="I24" t="n">
-        <v>111</v>
+        <v>110.0499999999993</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3867</v>
+        <v>0.3237</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0372</v>
+        <v>0.0444</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0237</v>
+        <v>0.0255</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0095</v>
+        <v>0.0113</v>
       </c>
       <c r="N24" t="n">
-        <v>8.140000216729245</v>
+        <v>9.184839315742089</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>+10426</t>
+          <t>+8750</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>-2.74817447802685</v>
+        <v>0.6979198033265082</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.03608817469521482</v>
+        <v>-2.218535999354475</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.183910751078082</v>
+        <v>0.3343300754021691</v>
       </c>
       <c r="T24" t="n">
-        <v>1.080791714011119</v>
+        <v>1.285179068259477</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09443943429775073</v>
+        <v>-3.142967471019861</v>
       </c>
     </row>
     <row r="25">
@@ -2357,24 +2357,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New York Rangers</t>
+          <t>Winnipeg Jets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>WPG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>89.1225</v>
+        <v>88.723</v>
       </c>
       <c r="F25" t="n">
-        <v>13.40335251852586</v>
+        <v>13.01841076713629</v>
       </c>
       <c r="G25" t="n">
         <v>67</v>
@@ -2383,45 +2383,45 @@
         <v>89</v>
       </c>
       <c r="I25" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3395</v>
+        <v>0.3758</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0522</v>
+        <v>0.0346</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0233</v>
+        <v>0.0236</v>
       </c>
       <c r="M25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="N25" t="n">
-        <v>7.823147646950697</v>
+        <v>8.140000216729245</v>
       </c>
       <c r="O25" t="n">
-        <v>8.699999999999999</v>
+        <v>-0.8</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>+11011</t>
+          <t>+9159</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>-4.799844584438726</v>
+        <v>-2.74817447802685</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.908540197038762</v>
+        <v>-0.03608817469521482</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4458023315861614</v>
+        <v>-2.183910751078082</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1363557253125856</v>
+        <v>1.080791714011119</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8318037149568038</v>
+        <v>0.09443943429775073</v>
       </c>
     </row>
     <row r="26">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>87.82940000000001</v>
+        <v>88.6086</v>
       </c>
       <c r="F26" t="n">
-        <v>13.27973383668051</v>
+        <v>13.22873032345119</v>
       </c>
       <c r="G26" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H26" t="n">
         <v>88</v>
@@ -2459,16 +2459,16 @@
         <v>110</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3901</v>
+        <v>0.4084</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0617</v>
+        <v>0.0684</v>
       </c>
       <c r="L26" t="n">
-        <v>0.024</v>
+        <v>0.0252</v>
       </c>
       <c r="M26" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0092</v>
       </c>
       <c r="N26" t="n">
         <v>6.925373482467831</v>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>+12558</t>
+          <t>+10770</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -2517,31 +2517,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>86.32299999999999</v>
+        <v>86.8292</v>
       </c>
       <c r="F27" t="n">
-        <v>13.2306982483017</v>
+        <v>13.18876118906435</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I27" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2575</v>
+        <v>0.2694</v>
       </c>
       <c r="K27" t="n">
-        <v>0.027</v>
+        <v>0.0292</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0152</v>
+        <v>0.0159</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0051</v>
+        <v>0.0054</v>
       </c>
       <c r="N27" t="n">
         <v>7.181298352106282</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>+19508</t>
+          <t>+18419</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>86.06999999999999</v>
+        <v>85.6073</v>
       </c>
       <c r="F28" t="n">
-        <v>13.05300494498525</v>
+        <v>13.035132457241</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H28" t="n">
         <v>86</v>
@@ -2605,16 +2605,16 @@
         <v>107</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3378</v>
+        <v>0.3232</v>
       </c>
       <c r="K28" t="n">
-        <v>0.047</v>
+        <v>0.0435</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0179</v>
+        <v>0.0188</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0066</v>
+        <v>0.0077</v>
       </c>
       <c r="N28" t="n">
         <v>7.118157267955309</v>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>+15052</t>
+          <t>+12887</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>84.5046</v>
+        <v>84.2174</v>
       </c>
       <c r="F29" t="n">
-        <v>13.2016441090009</v>
+        <v>13.15804129211732</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H29" t="n">
         <v>84</v>
@@ -2678,16 +2678,16 @@
         <v>106</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2955</v>
+        <v>0.2855</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0382</v>
+        <v>0.0359</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0138</v>
+        <v>0.0129</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0053</v>
+        <v>0.0041</v>
       </c>
       <c r="N29" t="n">
         <v>5.794809968760188</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>+18768</t>
+          <t>+24290</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>83.2178</v>
+        <v>83.2413</v>
       </c>
       <c r="F30" t="n">
-        <v>13.17292358406345</v>
+        <v>13.1236998388315</v>
       </c>
       <c r="G30" t="n">
         <v>62</v>
@@ -2751,16 +2751,16 @@
         <v>105</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1958</v>
+        <v>0.1942</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0185</v>
+        <v>0.0197</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0094</v>
+        <v>0.0101</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0037</v>
+        <v>0.0039</v>
       </c>
       <c r="N30" t="n">
         <v>5.904979974439156</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>+26927</t>
+          <t>+25541</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2795,71 +2795,71 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Calgary Flames</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>80.64570000000001</v>
+        <v>81.1888</v>
       </c>
       <c r="F31" t="n">
-        <v>13.13801477595551</v>
+        <v>12.92486207918586</v>
       </c>
       <c r="G31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H31" t="n">
         <v>81</v>
       </c>
       <c r="I31" t="n">
-        <v>102.0499999999993</v>
+        <v>103</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1786</v>
+        <v>0.2039</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0095</v>
+        <v>0.0221</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0053</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0024</v>
+        <v>0.0031</v>
       </c>
       <c r="N31" t="n">
-        <v>6.748602304917045</v>
+        <v>4.091492155309823</v>
       </c>
       <c r="O31" t="n">
-        <v>11.4</v>
+        <v>-0.6</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>+41567</t>
+          <t>+32158</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>-14.08048256211883</v>
+        <v>-7.566996579698094</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.4221108765379712</v>
+        <v>-0.1681206183302957</v>
       </c>
       <c r="S31" t="n">
-        <v>2.496371645999701</v>
+        <v>0.4355320155673481</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.8766338907976194</v>
+        <v>-0.9345974485237442</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.025233403433248</v>
+        <v>-3.769962061404637</v>
       </c>
     </row>
     <row r="32">
@@ -2868,71 +2868,71 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Calgary Flames</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>80.34690000000001</v>
+        <v>81.0604</v>
       </c>
       <c r="F32" t="n">
-        <v>12.98744885544414</v>
+        <v>13.08781421506635</v>
       </c>
       <c r="G32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H32" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I32" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1905</v>
+        <v>0.1828</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0212</v>
+        <v>0.0106</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0086</v>
+        <v>0.0065</v>
       </c>
       <c r="M32" t="n">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="N32" t="n">
-        <v>4.091492155309823</v>
+        <v>6.748602304917045</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.6</v>
+        <v>11.4</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>+33233</t>
+          <t>+38362</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>-7.566996579698094</v>
+        <v>-14.08048256211883</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.1681206183302957</v>
+        <v>-0.4221108765379712</v>
       </c>
       <c r="S32" t="n">
-        <v>0.4355320155673481</v>
+        <v>2.496371645999701</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.9345974485237442</v>
+        <v>-0.8766338907976194</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.769962061404637</v>
+        <v>-1.025233403433248</v>
       </c>
     </row>
     <row r="33">
@@ -2955,31 +2955,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>78.35809999999999</v>
+        <v>78.5949</v>
       </c>
       <c r="F33" t="n">
-        <v>12.89331951666505</v>
+        <v>12.86193363859775</v>
       </c>
       <c r="G33" t="n">
         <v>57</v>
       </c>
       <c r="H33" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I33" t="n">
         <v>99</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1563</v>
+        <v>0.1592</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0136</v>
+        <v>0.0128</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0054</v>
+        <v>0.0049</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0018</v>
+        <v>0.0015</v>
       </c>
       <c r="N33" t="n">
         <v>5.049701439462</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>+55456</t>
+          <t>+66567</t>
         </is>
       </c>
       <c r="Q33" t="n">
